--- a/xlsx/carteira_mensal/Mar_2026.xlsx
+++ b/xlsx/carteira_mensal/Mar_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="100">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -259,9 +259,6 @@
   </si>
   <si>
     <t>Regis Orsi</t>
-  </si>
-  <si>
-    <t>Mídias</t>
   </si>
   <si>
     <t>Phillipe Kafer Haacke de Oliveira</t>
@@ -1203,7 +1200,7 @@
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
         <v>717.0</v>
@@ -1247,7 +1244,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
@@ -1268,7 +1265,7 @@
         <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I44" t="n">
         <v>2652.0</v>
@@ -1294,34 +1291,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="51">
@@ -1329,39 +1326,39 @@
         <v>17</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Mar_2026.xlsx
+++ b/xlsx/carteira_mensal/Mar_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="116">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/03/2026 até 31/03/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,36 +153,105 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>Italo Marcos Castelani</t>
+  </si>
+  <si>
+    <t>Porta</t>
+  </si>
+  <si>
+    <t>23/05/25</t>
+  </si>
+  <si>
+    <t>KLEBER FRANCO BARBOSA</t>
+  </si>
+  <si>
+    <t>Orçamento 1</t>
+  </si>
+  <si>
+    <t>17/03/26</t>
+  </si>
+  <si>
+    <t>DANIELA IDA MENEGATTI MILANO</t>
+  </si>
+  <si>
+    <t>Já é Cliente</t>
+  </si>
+  <si>
+    <t>18/12/25</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES</t>
+  </si>
+  <si>
+    <t>Orçamento Assistência 2</t>
+  </si>
+  <si>
+    <t>20/03/26</t>
+  </si>
+  <si>
+    <t>51701-A1</t>
+  </si>
+  <si>
+    <t>Felipe Santiago Montenegro</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>23/02/26</t>
+  </si>
+  <si>
+    <t>11/03/26</t>
+  </si>
+  <si>
+    <t>Andrea beccaria</t>
+  </si>
+  <si>
+    <t>25/02/26</t>
+  </si>
+  <si>
+    <t>16/03/26</t>
+  </si>
+  <si>
+    <t>13/03/26</t>
+  </si>
+  <si>
+    <t>Cassio Braga</t>
+  </si>
+  <si>
+    <t>Parceiro</t>
+  </si>
+  <si>
+    <t>26/02/26</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>10/03/26</t>
+  </si>
+  <si>
+    <t>Izabel Aparecida Moreira da Cunha Haddad</t>
+  </si>
+  <si>
+    <t>Indicação de outros clientes</t>
+  </si>
+  <si>
+    <t>27/02/26</t>
+  </si>
+  <si>
     <t>Antonio Carlos Suematsu</t>
   </si>
   <si>
-    <t>Porta</t>
-  </si>
-  <si>
     <t>05/03/26</t>
   </si>
   <si>
-    <t>ERIC SERPA</t>
-  </si>
-  <si>
-    <t>Orçamento 1</t>
-  </si>
-  <si>
-    <t>16/03/26</t>
-  </si>
-  <si>
     <t>14/03/26</t>
   </si>
   <si>
     <t>Claudia Simone Santos</t>
   </si>
   <si>
-    <t>Indicação de outros clientes</t>
-  </si>
-  <si>
-    <t>10/03/26</t>
-  </si>
-  <si>
     <t>ROSANGELA PACHECO</t>
   </si>
   <si>
@@ -192,24 +261,12 @@
     <t>WILMA FERREIRA ASSAD</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>11/03/26</t>
-  </si>
-  <si>
     <t>23/03/26</t>
   </si>
   <si>
     <t>Silvana Visintin</t>
   </si>
   <si>
-    <t>Parceiro</t>
-  </si>
-  <si>
-    <t>13/03/26</t>
-  </si>
-  <si>
     <t>Julia Beatriz Bezerra Oliveira</t>
   </si>
   <si>
@@ -228,21 +285,12 @@
     <t>Marislaine silva de Godoi</t>
   </si>
   <si>
-    <t>Já é Cliente</t>
-  </si>
-  <si>
-    <t>20/03/26</t>
-  </si>
-  <si>
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
     <t>ANA CAROLINA NAPOLI LIMA</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
-  </si>
-  <si>
     <t>Carlos Alberto Nicolay Campeão Junior</t>
   </si>
   <si>
@@ -270,7 +318,7 @@
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>14</t>
+    <t>20</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -279,40 +327,40 @@
     <t>Pontuação Total</t>
   </si>
   <si>
-    <t>1.90</t>
+    <t>1.89</t>
   </si>
   <si>
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>303.693,10</t>
-  </si>
-  <si>
-    <t>211.017,32</t>
+    <t>493.107,08</t>
+  </si>
+  <si>
+    <t>342.960,59</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>197.369,04</t>
+    <t>318.476,36</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>191.642,72</t>
+    <t>306.429,44</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>13.648,28</t>
+    <t>24.484,23</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>14.524,77</t>
+    <t>21.449,57</t>
   </si>
 </sst>
 </file>
@@ -381,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O55"/>
+  <dimension ref="A2:O61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.22265625" customWidth="true" bestFit="true"/>
@@ -509,15 +557,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -525,7 +573,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -533,7 +581,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -639,7 +687,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>663.0</v>
+        <v>89.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -657,69 +705,69 @@
         <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>15408.0</v>
+        <v>1508.39</v>
       </c>
       <c r="J31" t="n">
-        <v>1560.61</v>
+        <v>0.0</v>
       </c>
       <c r="K31" t="n">
-        <v>13847.39</v>
+        <v>1508.39</v>
       </c>
       <c r="L31" t="n">
-        <v>13847.39</v>
+        <v>1508.39</v>
       </c>
       <c r="M31" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="N31" t="n">
-        <v>66301.0</v>
+        <v>8901.0</v>
       </c>
       <c r="O31" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="n">
+        <v>517.0</v>
+      </c>
+      <c r="D32" t="s">
         <v>54</v>
       </c>
-      <c r="C32" t="n">
-        <v>670.0</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>55</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G32" t="s">
         <v>56</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>50</v>
       </c>
       <c r="H32" t="s">
         <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>12180.0</v>
+        <v>1289.7</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0</v>
+        <v>55.41</v>
       </c>
       <c r="K32" t="n">
-        <v>12180.0</v>
+        <v>1234.29</v>
       </c>
       <c r="L32" t="n">
-        <v>12180.0</v>
+        <v>1234.29</v>
       </c>
       <c r="M32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="N32" t="n">
-        <v>67001.0</v>
+        <v>1.49</v>
+      </c>
+      <c r="N32" t="s">
+        <v>58</v>
       </c>
       <c r="O32" t="s">
         <v>57</v>
@@ -727,19 +775,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C33" t="n">
-        <v>675.0</v>
+        <v>633.0</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
@@ -748,45 +796,45 @@
         <v>50</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I33" t="n">
-        <v>35631.46</v>
+        <v>25000.0</v>
       </c>
       <c r="J33" t="n">
-        <v>4210.42</v>
+        <v>1212.9</v>
       </c>
       <c r="K33" t="n">
-        <v>31421.04</v>
+        <v>23787.1</v>
       </c>
       <c r="L33" t="n">
-        <v>31421.04</v>
+        <v>23219.62</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="N33" t="n">
-        <v>67501.0</v>
+        <v>63301.0</v>
       </c>
       <c r="O33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C34" t="n">
-        <v>673.0</v>
+        <v>637.0</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F34" t="n">
         <v>1.0</v>
@@ -795,92 +843,92 @@
         <v>50</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I34" t="n">
-        <v>27500.0</v>
+        <v>11798.32</v>
       </c>
       <c r="J34" t="n">
-        <v>2293.67</v>
+        <v>1539.79</v>
       </c>
       <c r="K34" t="n">
-        <v>25206.33</v>
+        <v>10258.53</v>
       </c>
       <c r="L34" t="n">
-        <v>22854.26</v>
+        <v>10258.53</v>
       </c>
       <c r="M34" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="N34" t="n">
-        <v>67301.0</v>
+        <v>63701.0</v>
       </c>
       <c r="O34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C35" t="n">
-        <v>685.0</v>
+        <v>643.0</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" t="s">
         <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="I35" t="n">
-        <v>27500.0</v>
+        <v>68346.86</v>
       </c>
       <c r="J35" t="n">
-        <v>2293.67</v>
+        <v>7334.39</v>
       </c>
       <c r="K35" t="n">
-        <v>25206.33</v>
+        <v>61012.47</v>
       </c>
       <c r="L35" t="n">
-        <v>22863.97</v>
+        <v>55259.35</v>
       </c>
       <c r="M35" t="n">
         <v>1.9</v>
       </c>
       <c r="N35" t="n">
-        <v>68501.0</v>
+        <v>64301.0</v>
       </c>
       <c r="O35" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C36" t="n">
-        <v>682.0</v>
+        <v>648.0</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
@@ -889,25 +937,25 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I36" t="n">
-        <v>19620.0</v>
+        <v>24000.0</v>
       </c>
       <c r="J36" t="n">
-        <v>566.91</v>
+        <v>693.46</v>
       </c>
       <c r="K36" t="n">
-        <v>19053.09</v>
+        <v>23306.54</v>
       </c>
       <c r="L36" t="n">
-        <v>18601.07</v>
+        <v>23306.54</v>
       </c>
       <c r="M36" t="n">
         <v>1.9</v>
       </c>
       <c r="N36" t="n">
-        <v>68201.0</v>
+        <v>64801.0</v>
       </c>
       <c r="O36" t="s">
         <v>66</v>
@@ -915,19 +963,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
       </c>
       <c r="C37" t="n">
-        <v>680.0</v>
+        <v>663.0</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F37" t="n">
         <v>1.0</v>
@@ -936,92 +984,92 @@
         <v>50</v>
       </c>
       <c r="H37" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I37" t="n">
-        <v>5640.0</v>
+        <v>15408.0</v>
       </c>
       <c r="J37" t="n">
-        <v>342.04</v>
+        <v>1560.61</v>
       </c>
       <c r="K37" t="n">
-        <v>5297.96</v>
+        <v>13847.39</v>
       </c>
       <c r="L37" t="n">
-        <v>5297.96</v>
+        <v>13847.39</v>
       </c>
       <c r="M37" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="N37" t="n">
-        <v>68001.0</v>
+        <v>66301.0</v>
       </c>
       <c r="O37" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C38" t="n">
-        <v>693.0</v>
+        <v>670.0</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G38" t="s">
         <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="I38" t="n">
-        <v>25151.2</v>
+        <v>12180.0</v>
       </c>
       <c r="J38" t="n">
-        <v>1080.67</v>
+        <v>0.0</v>
       </c>
       <c r="K38" t="n">
-        <v>24070.53</v>
+        <v>12180.0</v>
       </c>
       <c r="L38" t="n">
-        <v>23490.66</v>
+        <v>12180.0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="N38" t="n">
-        <v>69301.0</v>
+        <v>67001.0</v>
       </c>
       <c r="O38" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C39" t="n">
-        <v>698.0</v>
+        <v>675.0</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F39" t="n">
         <v>1.0</v>
@@ -1030,45 +1078,45 @@
         <v>50</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I39" t="n">
-        <v>900.0</v>
+        <v>35631.46</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0</v>
+        <v>4210.42</v>
       </c>
       <c r="K39" t="n">
-        <v>900.0</v>
+        <v>31421.04</v>
       </c>
       <c r="L39" t="n">
-        <v>900.0</v>
+        <v>31421.04</v>
       </c>
       <c r="M39" t="n">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="N39" t="n">
-        <v>69801.0</v>
+        <v>67501.0</v>
       </c>
       <c r="O39" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C40" t="n">
-        <v>701.0</v>
+        <v>673.0</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
@@ -1077,92 +1125,92 @@
         <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I40" t="n">
-        <v>3234.66</v>
+        <v>27500.0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0</v>
+        <v>2293.67</v>
       </c>
       <c r="K40" t="n">
-        <v>3234.66</v>
+        <v>25206.33</v>
       </c>
       <c r="L40" t="n">
-        <v>3234.66</v>
+        <v>22854.26</v>
       </c>
       <c r="M40" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="N40" t="n">
-        <v>70101.0</v>
+        <v>67301.0</v>
       </c>
       <c r="O40" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C41" t="n">
-        <v>703.0</v>
+        <v>685.0</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G41" t="s">
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I41" t="n">
-        <v>18500.0</v>
+        <v>27500.0</v>
       </c>
       <c r="J41" t="n">
-        <v>678.81</v>
+        <v>2293.67</v>
       </c>
       <c r="K41" t="n">
-        <v>17821.19</v>
+        <v>25206.33</v>
       </c>
       <c r="L41" t="n">
-        <v>17821.19</v>
+        <v>22863.97</v>
       </c>
       <c r="M41" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N41" t="n">
-        <v>70301.0</v>
+        <v>68501.0</v>
       </c>
       <c r="O41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C42" t="n">
-        <v>706.0</v>
+        <v>682.0</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
@@ -1171,92 +1219,92 @@
         <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I42" t="n">
-        <v>16800.0</v>
+        <v>19620.0</v>
       </c>
       <c r="J42" t="n">
-        <v>414.38</v>
+        <v>566.91</v>
       </c>
       <c r="K42" t="n">
-        <v>16385.62</v>
+        <v>19053.09</v>
       </c>
       <c r="L42" t="n">
-        <v>16385.62</v>
+        <v>18601.07</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N42" t="n">
-        <v>70601.0</v>
+        <v>68201.0</v>
       </c>
       <c r="O42" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C43" t="n">
-        <v>717.0</v>
+        <v>680.0</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="F43" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G43" t="s">
         <v>50</v>
       </c>
       <c r="H43" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I43" t="n">
-        <v>300.0</v>
+        <v>5640.0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0</v>
+        <v>342.04</v>
       </c>
       <c r="K43" t="n">
-        <v>300.0</v>
+        <v>5297.96</v>
       </c>
       <c r="L43" t="n">
-        <v>300.0</v>
+        <v>5297.96</v>
       </c>
       <c r="M43" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="N43" t="n">
-        <v>71701.0</v>
+        <v>68001.0</v>
       </c>
       <c r="O43" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C44" t="n">
-        <v>716.0</v>
+        <v>693.0</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
@@ -1265,100 +1313,382 @@
         <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I44" t="n">
+        <v>25151.2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1080.67</v>
+      </c>
+      <c r="K44" t="n">
+        <v>24070.53</v>
+      </c>
+      <c r="L44" t="n">
+        <v>23490.66</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="N44" t="n">
+        <v>69301.0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" t="n">
+        <v>698.0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" t="s">
+        <v>57</v>
+      </c>
+      <c r="I45" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N45" t="n">
+        <v>69801.0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" t="n">
+        <v>701.0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>50</v>
+      </c>
+      <c r="H46" t="s">
+        <v>82</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3234.66</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3234.66</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3234.66</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N46" t="n">
+        <v>70101.0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="n">
+        <v>703.0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>50</v>
+      </c>
+      <c r="H47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47" t="n">
+        <v>18500.0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>678.81</v>
+      </c>
+      <c r="K47" t="n">
+        <v>17821.19</v>
+      </c>
+      <c r="L47" t="n">
+        <v>17821.19</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N47" t="n">
+        <v>70301.0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" t="n">
+        <v>706.0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E48" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H48" t="s">
+        <v>96</v>
+      </c>
+      <c r="I48" t="n">
+        <v>16800.0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>414.38</v>
+      </c>
+      <c r="K48" t="n">
+        <v>16385.62</v>
+      </c>
+      <c r="L48" t="n">
+        <v>16385.62</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N48" t="n">
+        <v>70601.0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" t="n">
+        <v>717.0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>50</v>
+      </c>
+      <c r="H49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I49" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N49" t="n">
+        <v>71701.0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" t="n">
+        <v>716.0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" t="s">
+        <v>99</v>
+      </c>
+      <c r="I50" t="n">
         <v>2652.0</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J50" t="n">
         <v>207.1</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K50" t="n">
         <v>2444.9</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L50" t="n">
         <v>2444.9</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M50" t="n">
         <v>1.84</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N50" t="n">
         <v>71601.0</v>
       </c>
-      <c r="O44" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>93</v>
+      <c r="O50" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Mar_2026.xlsx
+++ b/xlsx/carteira_mensal/Mar_2026.xlsx
@@ -180,7 +180,7 @@
     <t>18/12/25</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>Orçamento Assistência 2</t>
